--- a/artfynd/A 19262-2025 artfynd.xlsx
+++ b/artfynd/A 19262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,323 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127419792</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79021</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr Märrtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>363676</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851141</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127419764</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79106</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr Märrtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>363676</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6851141</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127419757</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79040</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>184</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Broktagel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria bicolor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr Märrtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>363676</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6851141</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lodytor och block i SV brant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19262-2025 artfynd.xlsx
+++ b/artfynd/A 19262-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>127419792</v>
       </c>
       <c r="B6" t="n">
-        <v>79021</v>
+        <v>79024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127419764</v>
       </c>
       <c r="B7" t="n">
-        <v>79106</v>
+        <v>79109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127419757</v>
       </c>
       <c r="B8" t="n">
-        <v>79040</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19262-2025 artfynd.xlsx
+++ b/artfynd/A 19262-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>127419792</v>
       </c>
       <c r="B6" t="n">
-        <v>79024</v>
+        <v>79030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127419764</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127419757</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19262-2025 artfynd.xlsx
+++ b/artfynd/A 19262-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>127419792</v>
       </c>
       <c r="B6" t="n">
-        <v>79030</v>
+        <v>79033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127419764</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127419757</v>
       </c>
       <c r="B8" t="n">
-        <v>79049</v>
+        <v>79052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19262-2025 artfynd.xlsx
+++ b/artfynd/A 19262-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>127419792</v>
       </c>
       <c r="B6" t="n">
-        <v>79033</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127419764</v>
       </c>
       <c r="B7" t="n">
-        <v>79118</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127419757</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>79103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19262-2025 artfynd.xlsx
+++ b/artfynd/A 19262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419757</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66479921</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66479924</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66479922</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66479923</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419764</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,8 +1432,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127419792</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>